--- a/data/trans_orig/P17A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2007</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63106</t>
+          <t>63510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96198</t>
+          <t>98566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62248</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91264</t>
+          <t>91168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133278</t>
+          <t>132981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178053</t>
+          <t>175899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377578</t>
+          <t>375210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410670</t>
+          <t>410266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215416</t>
+          <t>215512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244432</t>
+          <t>245242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>602404</t>
+          <t>604558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647179</t>
+          <t>647476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48978</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78224</t>
+          <t>76877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81532</t>
+          <t>81646</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115669</t>
+          <t>115865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137747</t>
+          <t>140585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182840</t>
+          <t>185117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288710</t>
+          <t>290057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317956</t>
+          <t>316917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256196</t>
+          <t>256000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>290333</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>555959</t>
+          <t>553682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601052</t>
+          <t>598214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99682</t>
+          <t>97590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136749</t>
+          <t>135731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47245</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72745</t>
+          <t>73010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154784</t>
+          <t>154692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202076</t>
+          <t>200861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405640</t>
+          <t>406658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>442707</t>
+          <t>444799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95037</t>
+          <t>94772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120537</t>
+          <t>120360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>508095</t>
+          <t>509310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555387</t>
+          <t>555479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>259619</t>
+          <t>260602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320403</t>
+          <t>320950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198287</t>
+          <t>197707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>246255</t>
+          <t>248368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>475533</t>
+          <t>474176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>549342</t>
+          <t>550863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916113</t>
+          <t>915566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>976897</t>
+          <t>975914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>466018</t>
+          <t>463905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513986</t>
+          <t>514566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1399447</t>
+          <t>1397926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1473256</t>
+          <t>1474613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67572</t>
+          <t>68335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99358</t>
+          <t>100241</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177814</t>
+          <t>176043</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224156</t>
+          <t>222314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254859</t>
+          <t>251842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>310859</t>
+          <t>306806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251197</t>
+          <t>250314</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282983</t>
+          <t>282220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>344596</t>
+          <t>346438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390938</t>
+          <t>392709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>608448</t>
+          <t>612501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>664448</t>
+          <t>667465</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>35761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>360950</t>
+          <t>362273</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>425462</t>
+          <t>425943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>387024</t>
+          <t>383075</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>454458</t>
+          <t>450789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261812</t>
+          <t>261589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280786</t>
+          <t>280011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>823298</t>
+          <t>822817</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>887810</t>
+          <t>886487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1091652</t>
+          <t>1095321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1159086</t>
+          <t>1163035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>614212</t>
+          <t>612171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>708446</t>
+          <t>697989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>995451</t>
+          <t>997932</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1099895</t>
+          <t>1106023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1633802</t>
+          <t>1629141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1777659</t>
+          <t>1779363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2559075</t>
+          <t>2569532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2653309</t>
+          <t>2655350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2276217</t>
+          <t>2270089</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2380661</t>
+          <t>2378180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4865974</t>
+          <t>4864270</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5009831</t>
+          <t>5014492</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2012</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>62849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95968</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64049</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95810</t>
+          <t>97673</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134877</t>
+          <t>133389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182439</t>
+          <t>182104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340346</t>
+          <t>339273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373809</t>
+          <t>373465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215039</t>
+          <t>213176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246800</t>
+          <t>245520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564723</t>
+          <t>565058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>612285</t>
+          <t>613773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80422</t>
+          <t>79650</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119745</t>
+          <t>114922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80489</t>
+          <t>80103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113745</t>
+          <t>114935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170466</t>
+          <t>168401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220242</t>
+          <t>218921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297064</t>
+          <t>301887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>336387</t>
+          <t>337159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223362</t>
+          <t>222172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256618</t>
+          <t>257004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>533674</t>
+          <t>534995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583450</t>
+          <t>585515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136478</t>
+          <t>135192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183160</t>
+          <t>181032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77773</t>
+          <t>76262</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107596</t>
+          <t>108271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220397</t>
+          <t>221317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277840</t>
+          <t>275771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444293</t>
+          <t>446421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>490975</t>
+          <t>492261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151529</t>
+          <t>150854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181352</t>
+          <t>182863</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>608738</t>
+          <t>610807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>666181</t>
+          <t>665261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,04%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272450</t>
+          <t>270075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>335008</t>
+          <t>330789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>226619</t>
+          <t>224068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278894</t>
+          <t>277117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>511950</t>
+          <t>508176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>596134</t>
+          <t>591796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817864</t>
+          <t>822083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880422</t>
+          <t>882797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>486859</t>
+          <t>488636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>539134</t>
+          <t>541685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1322491</t>
+          <t>1326829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1406675</t>
+          <t>1410449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91253</t>
+          <t>91425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>129195</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>250206</t>
+          <t>252649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>305093</t>
+          <t>307801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354634</t>
+          <t>354502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>419766</t>
+          <t>424238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381541</t>
+          <t>380391</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418333</t>
+          <t>418161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>455460</t>
+          <t>452752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>510347</t>
+          <t>507904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>850373</t>
+          <t>845901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>915505</t>
+          <t>915637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50099</t>
+          <t>52093</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326024</t>
+          <t>327353</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>388312</t>
+          <t>389374</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>364089</t>
+          <t>360807</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>431244</t>
+          <t>428905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214861</t>
+          <t>212867</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237631</t>
+          <t>237047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>717356</t>
+          <t>716294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>779644</t>
+          <t>778315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>939384</t>
+          <t>941723</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1006539</t>
+          <t>1009821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>717117</t>
+          <t>727203</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>822235</t>
+          <t>828792</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1095914</t>
+          <t>1099846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1214272</t>
+          <t>1216422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1851757</t>
+          <t>1855084</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2004373</t>
+          <t>2013227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2585759</t>
+          <t>2579202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2690877</t>
+          <t>2680791</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2324782</t>
+          <t>2322632</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2443140</t>
+          <t>2439208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4942675</t>
+          <t>4933821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5095291</t>
+          <t>5091964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2016</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84962</t>
+          <t>85041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123453</t>
+          <t>122722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78735</t>
+          <t>80065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112298</t>
+          <t>113484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174085</t>
+          <t>174686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224424</t>
+          <t>224196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305639</t>
+          <t>306370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344130</t>
+          <t>344051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234757</t>
+          <t>233571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268320</t>
+          <t>266990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551723</t>
+          <t>551951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>602062</t>
+          <t>601461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76963</t>
+          <t>78599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>113676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77767</t>
+          <t>79137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114392</t>
+          <t>113434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165869</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214843</t>
+          <t>213656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266216</t>
+          <t>263551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300264</t>
+          <t>298628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257881</t>
+          <t>258839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294506</t>
+          <t>293136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>534657</t>
+          <t>535844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583631</t>
+          <t>585653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134438</t>
+          <t>135670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176110</t>
+          <t>179256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51395</t>
+          <t>50631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75595</t>
+          <t>77043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192961</t>
+          <t>192087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243189</t>
+          <t>242443</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345804</t>
+          <t>342658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387476</t>
+          <t>386244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90528</t>
+          <t>89080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114728</t>
+          <t>115492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>444847</t>
+          <t>445593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>495075</t>
+          <t>495949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>268191</t>
+          <t>265513</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>327226</t>
+          <t>323399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241580</t>
+          <t>242768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>295506</t>
+          <t>295341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526311</t>
+          <t>523592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>602429</t>
+          <t>609972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822412</t>
+          <t>826239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881447</t>
+          <t>884125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530370</t>
+          <t>530535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>584296</t>
+          <t>583108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1373085</t>
+          <t>1365542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1449203</t>
+          <t>1451922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145597</t>
+          <t>143094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190854</t>
+          <t>189658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>241715</t>
+          <t>242507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294732</t>
+          <t>293131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>399794</t>
+          <t>400652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>472933</t>
+          <t>471498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429852</t>
+          <t>431048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475109</t>
+          <t>477612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>443512</t>
+          <t>445113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>496529</t>
+          <t>495737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>886017</t>
+          <t>887452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>959156</t>
+          <t>958298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57845</t>
+          <t>56958</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>333635</t>
+          <t>335660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>402035</t>
+          <t>399305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>377045</t>
+          <t>375816</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>445003</t>
+          <t>450065</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229300</t>
+          <t>230187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253645</t>
+          <t>253339</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679990</t>
+          <t>682720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>748390</t>
+          <t>746365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924167</t>
+          <t>919105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>992125</t>
+          <t>993354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,55%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>806726</t>
+          <t>800313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>910161</t>
+          <t>903042</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1101684</t>
+          <t>1102313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1220035</t>
+          <t>1215256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1942789</t>
+          <t>1939272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2099044</t>
+          <t>2093439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2475561</t>
+          <t>2482680</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2578996</t>
+          <t>2585409</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2311561</t>
+          <t>2316340</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2429912</t>
+          <t>2429283</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4818274</t>
+          <t>4823879</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4974529</t>
+          <t>4978046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2023</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101410</t>
+          <t>100629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142135</t>
+          <t>140094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92926</t>
+          <t>93052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123086</t>
+          <t>122587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203639</t>
+          <t>202560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254421</t>
+          <t>253160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363077</t>
+          <t>365118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>403802</t>
+          <t>404583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324381</t>
+          <t>324880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>354541</t>
+          <t>354415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698258</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749040</t>
+          <t>750119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74801</t>
+          <t>75882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109202</t>
+          <t>110686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78091</t>
+          <t>76592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105282</t>
+          <t>104534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158826</t>
+          <t>159133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202869</t>
+          <t>203209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343011</t>
+          <t>341527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377412</t>
+          <t>376331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>277298</t>
+          <t>278046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>305988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>631924</t>
+          <t>631584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675967</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142309</t>
+          <t>143704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38917</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58970</t>
+          <t>58608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56711</t>
+          <t>51565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198341</t>
+          <t>196454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525955</t>
+          <t>524560</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636590</t>
+          <t>636643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107528</t>
+          <t>107890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127581</t>
+          <t>127703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636421</t>
+          <t>638308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>778051</t>
+          <t>783197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189259</t>
+          <t>190311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247555</t>
+          <t>248137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103977</t>
+          <t>102213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249680</t>
+          <t>247975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288794</t>
+          <t>288242</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>469843</t>
+          <t>469469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>786643</t>
+          <t>786061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>844939</t>
+          <t>843887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>727290</t>
+          <t>728995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>872993</t>
+          <t>874757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1541325</t>
+          <t>1541699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1722374</t>
+          <t>1722926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73358</t>
+          <t>73153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108087</t>
+          <t>105804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208856</t>
+          <t>207531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>433285</t>
+          <t>426867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>291672</t>
+          <t>293417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>526573</t>
+          <t>512050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366142</t>
+          <t>368425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400871</t>
+          <t>401076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407541</t>
+          <t>413959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>631970</t>
+          <t>633295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>788481</t>
+          <t>803004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1023382</t>
+          <t>1021637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48560</t>
+          <t>47027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>151794</t>
+          <t>153085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193069</t>
+          <t>194038</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>172286</t>
+          <t>170573</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>224507</t>
+          <t>226685</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191947</t>
+          <t>193480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229166</t>
+          <t>229394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>567264</t>
+          <t>566295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>608539</t>
+          <t>607248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,17 +10531,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>805152</t>
+          <t>805153</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>776333</t>
+          <t>774156</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>828554</t>
+          <t>830268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000840</t>
+          <t>1000841</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000840</t>
+          <t>1000841</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000840</t>
+          <t>1000841</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>459917</t>
+          <t>484416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>693638</t>
+          <t>689975</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>734996</t>
+          <t>733326</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1025828</t>
+          <t>1037066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1296159</t>
+          <t>1321708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1662410</t>
+          <t>1685446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2680985</t>
+          <t>2684648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2914706</t>
+          <t>2890207</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2548846</t>
+          <t>2537608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2839678</t>
+          <t>2841348</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5286887</t>
+          <t>5263851</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5653138</t>
+          <t>5627589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63510</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98566</t>
+          <t>97189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61438</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91168</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132981</t>
+          <t>133872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175899</t>
+          <t>178517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375210</t>
+          <t>376587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410266</t>
+          <t>410127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215512</t>
+          <t>215109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245242</t>
+          <t>246610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>604558</t>
+          <t>601940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647476</t>
+          <t>646585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>48074</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76877</t>
+          <t>78401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81646</t>
+          <t>81668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115865</t>
+          <t>116488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>140585</t>
+          <t>138628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185117</t>
+          <t>181380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>290057</t>
+          <t>288533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>316917</t>
+          <t>318860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256000</t>
+          <t>255377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>290219</t>
+          <t>290197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>553682</t>
+          <t>557419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>598214</t>
+          <t>600171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97590</t>
+          <t>99737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135731</t>
+          <t>138103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47422</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73010</t>
+          <t>70976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154692</t>
+          <t>156570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200861</t>
+          <t>200989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406658</t>
+          <t>404286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>444799</t>
+          <t>442652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94772</t>
+          <t>96806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120360</t>
+          <t>121002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509310</t>
+          <t>509182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555479</t>
+          <t>553601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>260602</t>
+          <t>262305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320950</t>
+          <t>318512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197707</t>
+          <t>194967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>248368</t>
+          <t>246159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>474176</t>
+          <t>477076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550863</t>
+          <t>553248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915566</t>
+          <t>918004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>975914</t>
+          <t>974211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463905</t>
+          <t>466114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>514566</t>
+          <t>517306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1397926</t>
+          <t>1395541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1474613</t>
+          <t>1471713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68335</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100241</t>
+          <t>100866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176043</t>
+          <t>178348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>222314</t>
+          <t>224702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251842</t>
+          <t>255824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>306806</t>
+          <t>309324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250314</t>
+          <t>249689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282220</t>
+          <t>281988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346438</t>
+          <t>344050</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392709</t>
+          <t>390404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>612501</t>
+          <t>609983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>667465</t>
+          <t>663483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,17%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>36431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>362273</t>
+          <t>360817</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>425943</t>
+          <t>426691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>383075</t>
+          <t>384684</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>450789</t>
+          <t>453144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261589</t>
+          <t>260919</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280011</t>
+          <t>280082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>822817</t>
+          <t>822069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>886487</t>
+          <t>887943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1095321</t>
+          <t>1092966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1163035</t>
+          <t>1161426</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>612171</t>
+          <t>611485</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>697989</t>
+          <t>703972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>997932</t>
+          <t>994407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1106023</t>
+          <t>1100709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1629141</t>
+          <t>1634748</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1779363</t>
+          <t>1781557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2569532</t>
+          <t>2563549</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2655350</t>
+          <t>2656036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2270089</t>
+          <t>2275403</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2378180</t>
+          <t>2381705</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4864270</t>
+          <t>4862076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5014492</t>
+          <t>5008885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62849</t>
+          <t>61762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>96574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65329</t>
+          <t>63677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97673</t>
+          <t>96904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>133389</t>
+          <t>134077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182104</t>
+          <t>183473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>339273</t>
+          <t>339740</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373465</t>
+          <t>374552</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213176</t>
+          <t>213945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245520</t>
+          <t>247172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>565058</t>
+          <t>563689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>613773</t>
+          <t>613085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79650</t>
+          <t>77853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114922</t>
+          <t>115717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80103</t>
+          <t>79771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114935</t>
+          <t>115059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>168401</t>
+          <t>168012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>218921</t>
+          <t>219781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>301887</t>
+          <t>301092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337159</t>
+          <t>338956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222172</t>
+          <t>222048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257004</t>
+          <t>257336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>534995</t>
+          <t>534135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>585515</t>
+          <t>585904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135192</t>
+          <t>134762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181032</t>
+          <t>179970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>78498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108271</t>
+          <t>109414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221317</t>
+          <t>220949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>275771</t>
+          <t>277612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446421</t>
+          <t>447483</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492261</t>
+          <t>492691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150854</t>
+          <t>149711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182863</t>
+          <t>180627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610807</t>
+          <t>608966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665261</t>
+          <t>665629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>270075</t>
+          <t>271921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>330789</t>
+          <t>332817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224068</t>
+          <t>223703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277117</t>
+          <t>276964</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>508176</t>
+          <t>510478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>591796</t>
+          <t>592945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822083</t>
+          <t>820055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882797</t>
+          <t>880951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488636</t>
+          <t>488789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>541685</t>
+          <t>542050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1326829</t>
+          <t>1325680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1410449</t>
+          <t>1408147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91425</t>
+          <t>90617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129195</t>
+          <t>126061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>252649</t>
+          <t>250708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>307801</t>
+          <t>303224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354502</t>
+          <t>353186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424238</t>
+          <t>419310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>380391</t>
+          <t>383525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418161</t>
+          <t>418969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452752</t>
+          <t>457329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>507904</t>
+          <t>509845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845901</t>
+          <t>850829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>915637</t>
+          <t>916953</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52093</t>
+          <t>50184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>327353</t>
+          <t>327008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>389374</t>
+          <t>389848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>360807</t>
+          <t>361055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>428905</t>
+          <t>427867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212867</t>
+          <t>214776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237047</t>
+          <t>237419</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>716294</t>
+          <t>715820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>778315</t>
+          <t>778660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941723</t>
+          <t>942761</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1009821</t>
+          <t>1009573</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>727203</t>
+          <t>725595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>828792</t>
+          <t>827005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1099846</t>
+          <t>1100203</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1216422</t>
+          <t>1213471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1855084</t>
+          <t>1853305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2013227</t>
+          <t>2003351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2579202</t>
+          <t>2580989</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2680791</t>
+          <t>2682399</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2322632</t>
+          <t>2325583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2439208</t>
+          <t>2438851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4933821</t>
+          <t>4943697</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5091964</t>
+          <t>5093743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>85158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122722</t>
+          <t>121156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80065</t>
+          <t>80259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113484</t>
+          <t>113857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174686</t>
+          <t>173615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224196</t>
+          <t>224330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306370</t>
+          <t>307936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344051</t>
+          <t>343934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233571</t>
+          <t>233198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266990</t>
+          <t>266796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551951</t>
+          <t>551817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601461</t>
+          <t>602532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78599</t>
+          <t>77814</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113676</t>
+          <t>110864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79137</t>
+          <t>79592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113434</t>
+          <t>113851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163847</t>
+          <t>167581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>213656</t>
+          <t>214471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263551</t>
+          <t>266363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298628</t>
+          <t>299413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>258839</t>
+          <t>258422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293136</t>
+          <t>292681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>535844</t>
+          <t>535029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>585653</t>
+          <t>581919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135670</t>
+          <t>135620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179256</t>
+          <t>179171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>50799</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77043</t>
+          <t>77644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192087</t>
+          <t>193867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242443</t>
+          <t>243582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>342658</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>386244</t>
+          <t>386294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89080</t>
+          <t>88479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115492</t>
+          <t>115324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445593</t>
+          <t>444454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>495949</t>
+          <t>494169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>265513</t>
+          <t>262496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>323399</t>
+          <t>321631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>242768</t>
+          <t>244300</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>295341</t>
+          <t>296501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>523592</t>
+          <t>520235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609972</t>
+          <t>602262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>826239</t>
+          <t>828007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884125</t>
+          <t>887142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530535</t>
+          <t>529375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>583108</t>
+          <t>581576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1365542</t>
+          <t>1373252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451922</t>
+          <t>1455279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>143377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189658</t>
+          <t>188762</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>242507</t>
+          <t>242394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293131</t>
+          <t>298465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400652</t>
+          <t>401593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>471498</t>
+          <t>470082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431048</t>
+          <t>431944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>477612</t>
+          <t>477329</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>445113</t>
+          <t>439779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495737</t>
+          <t>495850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>887452</t>
+          <t>888868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>958298</t>
+          <t>957357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33806</t>
+          <t>33323</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56958</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>335660</t>
+          <t>337775</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>399305</t>
+          <t>403249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>375816</t>
+          <t>379427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>450065</t>
+          <t>448760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230187</t>
+          <t>229779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253339</t>
+          <t>253822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>682720</t>
+          <t>678776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>746365</t>
+          <t>744250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>919105</t>
+          <t>920410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>993354</t>
+          <t>989743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,29%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>800313</t>
+          <t>809102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>903042</t>
+          <t>909277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1102313</t>
+          <t>1101236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1215256</t>
+          <t>1214739</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1939272</t>
+          <t>1945114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2093439</t>
+          <t>2092981</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2482680</t>
+          <t>2476445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2585409</t>
+          <t>2576620</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2316340</t>
+          <t>2316857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2429283</t>
+          <t>2430360</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4823879</t>
+          <t>4824337</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4978046</t>
+          <t>4972204</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>120285</t>
+          <t>131451</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100629</t>
+          <t>111767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140094</t>
+          <t>152270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>120381</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93052</t>
+          <t>106644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122587</t>
+          <t>136426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>251832</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>202560</t>
+          <t>225108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253160</t>
+          <t>277666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>384927</t>
+          <t>419167</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365118</t>
+          <t>398348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404583</t>
+          <t>438851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>340068</t>
+          <t>368030</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324880</t>
+          <t>351985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>354415</t>
+          <t>381767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>724995</t>
+          <t>787197</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>699519</t>
+          <t>761363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750119</t>
+          <t>813921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>97702</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75882</t>
+          <t>80654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110686</t>
+          <t>117967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>99795</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76592</t>
+          <t>85524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104534</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>181429</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159133</t>
+          <t>176434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203209</t>
+          <t>221284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>361253</t>
+          <t>385510</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341527</t>
+          <t>365245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376331</t>
+          <t>402558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>292111</t>
+          <t>323348</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278046</t>
+          <t>308887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305988</t>
+          <t>337619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>653364</t>
+          <t>708858</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>631584</t>
+          <t>685071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>729921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31621</t>
+          <t>79071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143704</t>
+          <t>113622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>43395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>65672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>134245</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51565</t>
+          <t>130354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196454</t>
+          <t>172268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>581793</t>
+          <t>374603</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524560</t>
+          <t>357990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636643</t>
+          <t>392541</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>118724</t>
+          <t>133442</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107890</t>
+          <t>121393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127703</t>
+          <t>143670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>700517</t>
+          <t>508045</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638308</t>
+          <t>486409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>783197</t>
+          <t>528323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166498</t>
+          <t>187065</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166498</t>
+          <t>187065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166498</t>
+          <t>187065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834762</t>
+          <t>658677</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834762</t>
+          <t>658677</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834762</t>
+          <t>658677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>231160</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190311</t>
+          <t>202375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248137</t>
+          <t>262867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>190368</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102213</t>
+          <t>193161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247975</t>
+          <t>238194</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>407683</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288242</t>
+          <t>413202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>469469</t>
+          <t>480868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>816883</t>
+          <t>900015</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>786061</t>
+          <t>868308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>843887</t>
+          <t>928800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>786602</t>
+          <t>643603</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>728995</t>
+          <t>621947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>874757</t>
+          <t>666980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1603485</t>
+          <t>1543618</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1541699</t>
+          <t>1510448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1722926</t>
+          <t>1578114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034198</t>
+          <t>1131175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034198</t>
+          <t>1131175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034198</t>
+          <t>1131175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976970</t>
+          <t>860141</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976970</t>
+          <t>860141</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976970</t>
+          <t>860141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011168</t>
+          <t>1991316</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011168</t>
+          <t>1991316</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011168</t>
+          <t>1991316</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89006</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73153</t>
+          <t>79934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>117504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>268680</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>207531</t>
+          <t>195924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>426867</t>
+          <t>237649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>357686</t>
+          <t>314091</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293417</t>
+          <t>284855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>512050</t>
+          <t>343944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>385223</t>
+          <t>471107</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368425</t>
+          <t>449554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401076</t>
+          <t>487124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>572146</t>
+          <t>612225</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>413959</t>
+          <t>592716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>633295</t>
+          <t>634441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>957368</t>
+          <t>1083332</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>803004</t>
+          <t>1053479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1021637</t>
+          <t>1112568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474229</t>
+          <t>567058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474229</t>
+          <t>567058</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474229</t>
+          <t>567058</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840826</t>
+          <t>830365</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840826</t>
+          <t>830365</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840826</t>
+          <t>830365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1315054</t>
+          <t>1397423</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1315054</t>
+          <t>1397423</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1315054</t>
+          <t>1397423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47027</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>172399</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153085</t>
+          <t>174860</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194038</t>
+          <t>221973</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>195688</t>
+          <t>216105</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170573</t>
+          <t>192441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>226685</t>
+          <t>243013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>217218</t>
+          <t>215812</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>193480</t>
+          <t>197855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229394</t>
+          <t>225905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>587934</t>
+          <t>647401</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>566295</t>
+          <t>620117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607248</t>
+          <t>667230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>805153</t>
+          <t>863213</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>774156</t>
+          <t>836305</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>830268</t>
+          <t>886877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760333</t>
+          <t>842090</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760333</t>
+          <t>842090</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760333</t>
+          <t>842090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000841</t>
+          <t>1079318</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000841</t>
+          <t>1079318</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000841</t>
+          <t>1079318</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>627326</t>
+          <t>674690</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>484416</t>
+          <t>630080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>689975</t>
+          <t>729958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>877089</t>
+          <t>903166</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>733326</t>
+          <t>858427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1037066</t>
+          <t>950215</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1504415</t>
+          <t>1577856</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1321708</t>
+          <t>1515139</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1685446</t>
+          <t>1650392</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2747297</t>
+          <t>2766212</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2684648</t>
+          <t>2710944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2890207</t>
+          <t>2810822</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2697585</t>
+          <t>2728049</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2537608</t>
+          <t>2681000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2841348</t>
+          <t>2772788</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5444882</t>
+          <t>5494261</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5263851</t>
+          <t>5421725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5627589</t>
+          <t>5556978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374623</t>
+          <t>3440902</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374623</t>
+          <t>3440902</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374623</t>
+          <t>3440902</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574674</t>
+          <t>3631215</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574674</t>
+          <t>3631215</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574674</t>
+          <t>3631215</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6949297</t>
+          <t>7072117</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6949297</t>
+          <t>7072117</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6949297</t>
+          <t>7072117</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
